--- a/outputs/portfolio_combined/factor_returns.xlsx
+++ b/outputs/portfolio_combined/factor_returns.xlsx
@@ -1032,7 +1032,7 @@
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>-0.0003505160688425158</v>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="n">
@@ -1055,7 +1055,7 @@
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>0.0007276708475944316</v>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="n">
@@ -1078,7 +1078,7 @@
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="n">
-        <v>0.001050324551129321</v>
+        <v>0.003795793500031102</v>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="n">
@@ -1101,7 +1101,7 @@
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="n">
-        <v>5.109073702265818e-05</v>
+        <v>0.002914143800819856</v>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="n">
@@ -1124,7 +1124,7 @@
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>-0.00321033251535626</v>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="n">
@@ -1147,7 +1147,7 @@
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="n">
-        <v>0.002429315258463274</v>
+        <v>0.004129165072297688</v>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="n">
@@ -1170,7 +1170,7 @@
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>-0.001048906784669553</v>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="n">
@@ -1193,7 +1193,7 @@
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="n">
-        <v>0.001431957560462685</v>
+        <v>0.006230689823961966</v>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="n">
@@ -1216,7 +1216,7 @@
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="n">
-        <v>0.001768649893054411</v>
+        <v>0.003497552848327398</v>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="n">
@@ -1239,7 +1239,7 @@
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="n">
-        <v>2.167788798593291e-05</v>
+        <v>0.002350034315336401</v>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="n">
@@ -1262,7 +1262,7 @@
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="n">
-        <v>0.0003822073351156436</v>
+        <v>0.003058654928036421</v>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="n">
@@ -1285,7 +1285,7 @@
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="n">
-        <v>0.0005134009340455237</v>
+        <v>0.0009397731148197081</v>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="n">
@@ -1308,7 +1308,7 @@
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="n">
-        <v>0</v>
+        <v>0.00546268623255154</v>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="n">
@@ -1331,7 +1331,7 @@
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="n">
-        <v>0</v>
+        <v>0.00098779378412577</v>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="n">
@@ -1354,7 +1354,7 @@
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="n">
-        <v>-0.00138481355759764</v>
+        <v>-0.0004882236260403448</v>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="n">
@@ -1377,7 +1377,7 @@
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="n">
-        <v>0</v>
+        <v>0.001041686320120928</v>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="n">
@@ -1400,7 +1400,7 @@
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="n">
-        <v>0</v>
+        <v>0.0005574067263558502</v>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="n">
@@ -1423,7 +1423,7 @@
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="n">
-        <v>-0.001175902576038587</v>
+        <v>-0.003184592813322364</v>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="n">
@@ -1446,7 +1446,7 @@
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>0.002726601185508594</v>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="n">
@@ -1469,7 +1469,7 @@
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="n">
-        <v>0</v>
+        <v>-0.002690059503812629</v>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="n">
@@ -1492,7 +1492,7 @@
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="n">
-        <v>-0.002727601527541945</v>
+        <v>-0.0009310588369549479</v>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="n">
@@ -1515,7 +1515,7 @@
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="n">
-        <v>0.002473235469252915</v>
+        <v>0.003880133258832556</v>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="n">
@@ -1538,7 +1538,7 @@
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="n">
-        <v>0.0004661378240420959</v>
+        <v>-0.001402463003770399</v>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
@@ -1561,7 +1561,7 @@
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="n">
-        <v>-0.002275160744537534</v>
+        <v>-0.0004720506054531487</v>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
@@ -1584,7 +1584,7 @@
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="n">
-        <v>0.005900868884022044</v>
+        <v>0.006943869454561985</v>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
@@ -1607,7 +1607,7 @@
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="n">
-        <v>0</v>
+        <v>0.0003502722428037167</v>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
@@ -1630,7 +1630,7 @@
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="n">
-        <v>9.238950367328961e-05</v>
+        <v>0.004450009055087601</v>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="n">
@@ -1653,7 +1653,7 @@
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="n">
-        <v>0</v>
+        <v>0.00146262492522014</v>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="n">
@@ -1676,7 +1676,7 @@
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="n">
-        <v>0</v>
+        <v>-0.002020400481541916</v>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
@@ -1699,7 +1699,7 @@
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="n">
-        <v>0.0009518083335967696</v>
+        <v>0.001113695123381632</v>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="n">
@@ -1722,7 +1722,7 @@
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="n">
-        <v>0</v>
+        <v>-0.003882130388153683</v>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="n">
@@ -1745,7 +1745,7 @@
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="n">
-        <v>0</v>
+        <v>-0.003243709610228391</v>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="n">
@@ -1768,7 +1768,7 @@
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="n">
-        <v>0.001981555580526884</v>
+        <v>0.005252752105660478</v>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="n">
@@ -1791,7 +1791,7 @@
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="n">
-        <v>0</v>
+        <v>-0.0004382351988738057</v>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="n">
@@ -1814,7 +1814,7 @@
       <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="n">
-        <v>0</v>
+        <v>-0.00257895617965294</v>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="n">
@@ -1837,7 +1837,7 @@
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="n">
-        <v>-0.002791481397298529</v>
+        <v>-0.009455135462746405</v>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="n">
@@ -1860,7 +1860,7 @@
       <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="n">
-        <v>0</v>
+        <v>0.001608666890112789</v>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="n">
@@ -1883,7 +1883,7 @@
       <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="n">
-        <v>0</v>
+        <v>0.008367238027009141</v>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="n">
@@ -1906,7 +1906,7 @@
       <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="n">
-        <v>0.0002301625388884053</v>
+        <v>0.002004101731745219</v>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="n">
@@ -1929,7 +1929,7 @@
       <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="n">
-        <v>0</v>
+        <v>0.0007935863640779158</v>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="n">
@@ -1952,7 +1952,7 @@
       <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="n">
-        <v>0</v>
+        <v>-0.004695661026902389</v>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
@@ -1975,7 +1975,7 @@
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="n">
-        <v>0.002571454078953921</v>
+        <v>0.006199169842802565</v>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
@@ -1998,7 +1998,7 @@
       <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="n">
-        <v>0</v>
+        <v>0.00280746747094435</v>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
@@ -2021,7 +2021,7 @@
       <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="n">
-        <v>0</v>
+        <v>0.0008739872866251324</v>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
@@ -2044,7 +2044,7 @@
       <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="n">
-        <v>-0.0008691004457344398</v>
+        <v>-0.001571008944748438</v>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="n">
@@ -2067,7 +2067,7 @@
       <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="n">
-        <v>0</v>
+        <v>0.003196298717450518</v>
       </c>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="n">
@@ -2090,7 +2090,7 @@
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="n">
-        <v>0</v>
+        <v>0.003979937534913282</v>
       </c>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="n">
@@ -2113,7 +2113,7 @@
       <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="n">
-        <v>0.001664680352085855</v>
+        <v>0.00471544135265666</v>
       </c>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="n">
@@ -2136,7 +2136,7 @@
       <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="n">
-        <v>0.0006257439369877003</v>
+        <v>0.005167038017633353</v>
       </c>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="n">
@@ -2159,7 +2159,7 @@
       <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="n">
-        <v>0</v>
+        <v>0.002184590112058248</v>
       </c>
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="n">
@@ -2182,7 +2182,7 @@
       <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="n">
-        <v>0.0007276492000771467</v>
+        <v>0.001950549130911966</v>
       </c>
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="n">
@@ -2205,7 +2205,7 @@
       <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="n">
-        <v>0.0004821268660174517</v>
+        <v>0.003704507003489468</v>
       </c>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="n">
@@ -2228,7 +2228,7 @@
       <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="n">
-        <v>0</v>
+        <v>0.0006190666020128486</v>
       </c>
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="n">
@@ -2251,7 +2251,7 @@
       <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="n">
-        <v>0.0008326604166612064</v>
+        <v>0.004876493638910784</v>
       </c>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="n">
@@ -2274,7 +2274,7 @@
       <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="n">
-        <v>0.0003437550559138694</v>
+        <v>0.001006166792368421</v>
       </c>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="n">
@@ -2297,7 +2297,7 @@
       <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="n">
-        <v>0.0009461175462728278</v>
+        <v>0.004129471563751397</v>
       </c>
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="n">
@@ -2320,7 +2320,7 @@
       <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="n">
-        <v>0.0009143330289407293</v>
+        <v>0.0006522847296856309</v>
       </c>
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="n">
@@ -2343,7 +2343,7 @@
       <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="n">
-        <v>0.002692066205806687</v>
+        <v>0.00153465269126071</v>
       </c>
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="n">
@@ -2366,7 +2366,7 @@
       <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="n">
-        <v>-6.029599405382353e-06</v>
+        <v>0.0003783133110789932</v>
       </c>
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="n">
@@ -2389,7 +2389,7 @@
       <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="n">
-        <v>0.001555279656052503</v>
+        <v>0.00461579244823954</v>
       </c>
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="n">
@@ -2412,7 +2412,7 @@
       <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="n">
-        <v>0</v>
+        <v>-0.00296689842152868</v>
       </c>
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="n">
@@ -2437,7 +2437,7 @@
       </c>
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="n">
-        <v>0</v>
+        <v>-0.002445653029737285</v>
       </c>
       <c r="F99" t="n">
         <v>-0.01797143418240255</v>
@@ -2464,7 +2464,7 @@
       </c>
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="n">
-        <v>-0.0005910304996390869</v>
+        <v>0.0001057668296193021</v>
       </c>
       <c r="F100" t="n">
         <v>-0.0155959346377546</v>
@@ -2491,7 +2491,7 @@
       </c>
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="n">
-        <v>0</v>
+        <v>-0.001193645458025317</v>
       </c>
       <c r="F101" t="n">
         <v>-0.04923449790023127</v>
@@ -2518,7 +2518,7 @@
       </c>
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="n">
-        <v>0</v>
+        <v>0.000503934949780636</v>
       </c>
       <c r="F102" t="n">
         <v>0.0151294758714926</v>
@@ -2545,7 +2545,7 @@
       </c>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="n">
-        <v>0.0008540417604828783</v>
+        <v>0.0006944842691797634</v>
       </c>
       <c r="F103" t="n">
         <v>0.005761648977983758</v>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="D104" t="inlineStr"/>
       <c r="E104" t="n">
-        <v>0</v>
+        <v>-0.0005743209525756331</v>
       </c>
       <c r="F104" t="n">
         <v>-0.01002965024863872</v>
@@ -2599,7 +2599,7 @@
       </c>
       <c r="D105" t="inlineStr"/>
       <c r="E105" t="n">
-        <v>0</v>
+        <v>0.0004682888056149804</v>
       </c>
       <c r="F105" t="n">
         <v>0.01410850461935209</v>
@@ -2626,7 +2626,7 @@
       </c>
       <c r="D106" t="inlineStr"/>
       <c r="E106" t="n">
-        <v>-0.0014259772346083</v>
+        <v>-0.007548522436377778</v>
       </c>
       <c r="F106" t="n">
         <v>0.06470193928395651</v>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="n">
-        <v>0</v>
+        <v>-0.0007617429906892563</v>
       </c>
       <c r="F107" t="n">
         <v>0.04048396029673373</v>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="D108" t="inlineStr"/>
       <c r="E108" t="n">
-        <v>0</v>
+        <v>-0.006966138839686483</v>
       </c>
       <c r="F108" t="n">
         <v>0.03564529184231058</v>
@@ -2707,7 +2707,7 @@
       </c>
       <c r="D109" t="inlineStr"/>
       <c r="E109" t="n">
-        <v>0.002694730956766983</v>
+        <v>0.009747005983749306</v>
       </c>
       <c r="F109" t="n">
         <v>-0.08543493406067182</v>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="n">
-        <v>0</v>
+        <v>0.005681350034502814</v>
       </c>
       <c r="F110" t="n">
         <v>-0.0303624921578623</v>
@@ -2761,7 +2761,7 @@
       </c>
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="n">
-        <v>0.001177609045681055</v>
+        <v>-0.000630455941160805</v>
       </c>
       <c r="F111" t="n">
         <v>0.005948687857018964</v>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="n">
-        <v>0.00140362724460402</v>
+        <v>0.003391656904738798</v>
       </c>
       <c r="F112" t="n">
         <v>-0.03673347648416109</v>
@@ -2815,7 +2815,7 @@
       </c>
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="n">
-        <v>0</v>
+        <v>-0.007418048448013061</v>
       </c>
       <c r="F113" t="n">
         <v>0.09382468455921844</v>
@@ -2842,7 +2842,7 @@
       </c>
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="n">
-        <v>0</v>
+        <v>0.006897330046136928</v>
       </c>
       <c r="F114" t="n">
         <v>-0.05138305515675989</v>
@@ -2869,7 +2869,7 @@
       </c>
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="n">
-        <v>0.0002514198012653968</v>
+        <v>0.002614272373831268</v>
       </c>
       <c r="F115" t="n">
         <v>-0.01611500011289002</v>
@@ -2896,7 +2896,7 @@
       </c>
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="n">
-        <v>0</v>
+        <v>-0.004007452069296331</v>
       </c>
       <c r="F116" t="n">
         <v>0.07014757113162562</v>
@@ -2923,7 +2923,7 @@
       </c>
       <c r="D117" t="inlineStr"/>
       <c r="E117" t="n">
-        <v>0</v>
+        <v>0.004680780169768015</v>
       </c>
       <c r="F117" t="n">
         <v>-0.002445810251188008</v>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="D118" t="inlineStr"/>
       <c r="E118" t="n">
-        <v>0.0009030676363967058</v>
+        <v>0.002337552888943068</v>
       </c>
       <c r="F118" t="n">
         <v>-0.02745230095780676</v>
@@ -2977,7 +2977,7 @@
       </c>
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="n">
-        <v>0</v>
+        <v>0.004025695172958015</v>
       </c>
       <c r="F119" t="n">
         <v>-0.06186473659121106</v>
@@ -3004,7 +3004,7 @@
       </c>
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="n">
-        <v>0</v>
+        <v>0.00310566073272524</v>
       </c>
       <c r="F120" t="n">
         <v>-0.04030944241502982</v>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="D121" t="inlineStr"/>
       <c r="E121" t="n">
-        <v>3.525431608342731e-05</v>
+        <v>0.0003967025668916547</v>
       </c>
       <c r="F121" t="n">
         <v>0.048051667779897</v>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="D122" t="inlineStr"/>
       <c r="E122" t="n">
-        <v>0</v>
+        <v>-0.009859687199706247</v>
       </c>
       <c r="F122" t="n">
         <v>-0.02048206568410926</v>
@@ -3085,7 +3085,7 @@
       </c>
       <c r="D123" t="inlineStr"/>
       <c r="E123" t="n">
-        <v>0</v>
+        <v>-0.01693104221479366</v>
       </c>
       <c r="F123" t="n">
         <v>0.09427726232663836</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="D124" t="inlineStr"/>
       <c r="E124" t="n">
-        <v>0.002411027941928178</v>
+        <v>0.01734805229320634</v>
       </c>
       <c r="F124" t="n">
         <v>-0.2076761273496234</v>
@@ -3139,7 +3139,7 @@
       </c>
       <c r="D125" t="inlineStr"/>
       <c r="E125" t="n">
-        <v>0</v>
+        <v>0.006818550951268635</v>
       </c>
       <c r="F125" t="n">
         <v>-0.03757078816932224</v>
@@ -3166,7 +3166,7 @@
       </c>
       <c r="D126" t="inlineStr"/>
       <c r="E126" t="n">
-        <v>0.005284723465446721</v>
+        <v>0.005781448636716062</v>
       </c>
       <c r="F126" t="n">
         <v>-0.0626436987007794</v>
@@ -3193,7 +3193,7 @@
       </c>
       <c r="D127" t="inlineStr"/>
       <c r="E127" t="n">
-        <v>0.00450942680492215</v>
+        <v>0.004990521330494564</v>
       </c>
       <c r="F127" t="n">
         <v>-0.003171517695337467</v>
@@ -3220,7 +3220,7 @@
       </c>
       <c r="D128" t="inlineStr"/>
       <c r="E128" t="n">
-        <v>0</v>
+        <v>0.004488371632808201</v>
       </c>
       <c r="F128" t="n">
         <v>-0.0792273332409657</v>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="D129" t="inlineStr"/>
       <c r="E129" t="n">
-        <v>0</v>
+        <v>-0.002547282505611131</v>
       </c>
       <c r="F129" t="n">
         <v>0.0388316151314837</v>
@@ -3274,7 +3274,7 @@
       </c>
       <c r="D130" t="inlineStr"/>
       <c r="E130" t="n">
-        <v>-0.001256106868246381</v>
+        <v>-0.002775138229323116</v>
       </c>
       <c r="F130" t="n">
         <v>-0.02640252132463428</v>
@@ -3301,7 +3301,7 @@
       </c>
       <c r="D131" t="inlineStr"/>
       <c r="E131" t="n">
-        <v>0</v>
+        <v>0.01837999556501554</v>
       </c>
       <c r="F131" t="n">
         <v>-0.2095756649651593</v>
@@ -3328,7 +3328,7 @@
       </c>
       <c r="D132" t="inlineStr"/>
       <c r="E132" t="n">
-        <v>0</v>
+        <v>0.005319909524146918</v>
       </c>
       <c r="F132" t="n">
         <v>-0.08325434903979645</v>
@@ -3355,7 +3355,7 @@
       </c>
       <c r="D133" t="inlineStr"/>
       <c r="E133" t="n">
-        <v>-0.0005277260550679002</v>
+        <v>0.0009810385825841474</v>
       </c>
       <c r="F133" t="n">
         <v>-0.03167326517527558</v>
@@ -3382,7 +3382,7 @@
       </c>
       <c r="D134" t="inlineStr"/>
       <c r="E134" t="n">
-        <v>0</v>
+        <v>0.006392141731224831</v>
       </c>
       <c r="F134" t="n">
         <v>-0.1667169578151463</v>
@@ -3409,7 +3409,7 @@
       </c>
       <c r="D135" t="inlineStr"/>
       <c r="E135" t="n">
-        <v>0</v>
+        <v>0.004751772735293249</v>
       </c>
       <c r="F135" t="n">
         <v>0.06008674583313556</v>
@@ -3436,7 +3436,7 @@
       </c>
       <c r="D136" t="inlineStr"/>
       <c r="E136" t="n">
-        <v>0.0004653869778174627</v>
+        <v>0.002061663216096068</v>
       </c>
       <c r="F136" t="n">
         <v>0.008357739033213352</v>
@@ -3463,7 +3463,7 @@
       </c>
       <c r="D137" t="inlineStr"/>
       <c r="E137" t="n">
-        <v>0</v>
+        <v>0.003625605582075498</v>
       </c>
       <c r="F137" t="n">
         <v>-0.02197257927042995</v>
@@ -3490,7 +3490,7 @@
       </c>
       <c r="D138" t="inlineStr"/>
       <c r="E138" t="n">
-        <v>0</v>
+        <v>-0.0009578539029881995</v>
       </c>
       <c r="F138" t="n">
         <v>-0.00204013940425668</v>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="D139" t="inlineStr"/>
       <c r="E139" t="n">
-        <v>0.0005348124795830639</v>
+        <v>-0.0033746450410843</v>
       </c>
       <c r="F139" t="n">
         <v>0.07089012793408611</v>
@@ -3544,7 +3544,7 @@
       </c>
       <c r="D140" t="inlineStr"/>
       <c r="E140" t="n">
-        <v>0</v>
+        <v>0.003468547652345077</v>
       </c>
       <c r="F140" t="n">
         <v>-0.01611922643101132</v>
@@ -3571,7 +3571,7 @@
       </c>
       <c r="D141" t="inlineStr"/>
       <c r="E141" t="n">
-        <v>0</v>
+        <v>-0.002670199241254517</v>
       </c>
       <c r="F141" t="n">
         <v>-0.06859669846145716</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="D142" t="inlineStr"/>
       <c r="E142" t="n">
-        <v>0.001701725234082771</v>
+        <v>0.0004077258618800286</v>
       </c>
       <c r="F142" t="n">
         <v>-0.00998038754964814</v>
@@ -3625,7 +3625,7 @@
       </c>
       <c r="D143" t="inlineStr"/>
       <c r="E143" t="n">
-        <v>0</v>
+        <v>-0.004565336948677572</v>
       </c>
       <c r="F143" t="n">
         <v>0.0320316054694284</v>
@@ -3652,7 +3652,7 @@
       </c>
       <c r="D144" t="inlineStr"/>
       <c r="E144" t="n">
-        <v>0</v>
+        <v>0.006982692120436127</v>
       </c>
       <c r="F144" t="n">
         <v>0.04138892365497804</v>
@@ -3679,7 +3679,7 @@
       </c>
       <c r="D145" t="inlineStr"/>
       <c r="E145" t="n">
-        <v>-0.001743942330466818</v>
+        <v>-0.002789803145129749</v>
       </c>
       <c r="F145" t="n">
         <v>-0.01305812598125544</v>
@@ -3706,7 +3706,7 @@
       </c>
       <c r="D146" t="inlineStr"/>
       <c r="E146" t="n">
-        <v>0</v>
+        <v>-0.002453267530260727</v>
       </c>
       <c r="F146" t="n">
         <v>-0.02412469459907413</v>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="D147" t="inlineStr"/>
       <c r="E147" t="n">
-        <v>0</v>
+        <v>0.00325256983765454</v>
       </c>
       <c r="F147" t="n">
         <v>0.01299330780616825</v>
@@ -3760,7 +3760,7 @@
       </c>
       <c r="D148" t="inlineStr"/>
       <c r="E148" t="n">
-        <v>-0.001062362371294637</v>
+        <v>-0.006553709645996379</v>
       </c>
       <c r="F148" t="n">
         <v>0.06632017572164661</v>
@@ -3787,7 +3787,7 @@
       </c>
       <c r="D149" t="inlineStr"/>
       <c r="E149" t="n">
-        <v>0</v>
+        <v>0.001433200839993905</v>
       </c>
       <c r="F149" t="n">
         <v>-0.05557966825027738</v>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="D150" t="inlineStr"/>
       <c r="E150" t="n">
-        <v>0</v>
+        <v>-0.01172237090442355</v>
       </c>
       <c r="F150" t="n">
         <v>0.1257818568409853</v>
@@ -3841,7 +3841,7 @@
       </c>
       <c r="D151" t="inlineStr"/>
       <c r="E151" t="n">
-        <v>0.002363823028106078</v>
+        <v>0.01057540894572015</v>
       </c>
       <c r="F151" t="n">
         <v>-0.07967256674568374</v>
@@ -3868,7 +3868,7 @@
       </c>
       <c r="D152" t="inlineStr"/>
       <c r="E152" t="n">
-        <v>0</v>
+        <v>-0.003246817330126493</v>
       </c>
       <c r="F152" t="n">
         <v>-0.009568910412397325</v>
@@ -3895,7 +3895,7 @@
       </c>
       <c r="D153" t="inlineStr"/>
       <c r="E153" t="n">
-        <v>0</v>
+        <v>-0.008297920289607307</v>
       </c>
       <c r="F153" t="n">
         <v>0.02236971942645938</v>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="D154" t="inlineStr"/>
       <c r="E154" t="n">
-        <v>0.003505037987519152</v>
+        <v>0.01567301503004542</v>
       </c>
       <c r="F154" t="n">
         <v>-0.09271494545983905</v>
@@ -3949,7 +3949,7 @@
       </c>
       <c r="D155" t="inlineStr"/>
       <c r="E155" t="n">
-        <v>0</v>
+        <v>0.011913114236258</v>
       </c>
       <c r="F155" t="n">
         <v>-0.05443839041870296</v>
@@ -3976,7 +3976,7 @@
       </c>
       <c r="D156" t="inlineStr"/>
       <c r="E156" t="n">
-        <v>0</v>
+        <v>-0.002107603053654497</v>
       </c>
       <c r="F156" t="n">
         <v>0.03424812105377184</v>
@@ -4003,7 +4003,7 @@
       </c>
       <c r="D157" t="inlineStr"/>
       <c r="E157" t="n">
-        <v>0.002960255277207511</v>
+        <v>0.01349099556600592</v>
       </c>
       <c r="F157" t="n">
         <v>-0.1327497161448376</v>
@@ -4030,7 +4030,7 @@
       </c>
       <c r="D158" t="inlineStr"/>
       <c r="E158" t="n">
-        <v>0</v>
+        <v>-0.001584566007583001</v>
       </c>
       <c r="F158" t="n">
         <v>-0.0133338208379421</v>
@@ -4057,7 +4057,7 @@
       </c>
       <c r="D159" t="inlineStr"/>
       <c r="E159" t="n">
-        <v>0</v>
+        <v>-0.0001577958141125531</v>
       </c>
       <c r="F159" t="n">
         <v>0.05165303310514513</v>
@@ -4084,7 +4084,7 @@
       </c>
       <c r="D160" t="inlineStr"/>
       <c r="E160" t="n">
-        <v>0.0008975522917683841</v>
+        <v>-0.001185508566042713</v>
       </c>
       <c r="F160" t="n">
         <v>0.05034411977574393</v>
@@ -4111,7 +4111,7 @@
       </c>
       <c r="D161" t="inlineStr"/>
       <c r="E161" t="n">
-        <v>0</v>
+        <v>-0.002267936966916607</v>
       </c>
       <c r="F161" t="n">
         <v>-0.04150452981980568</v>
@@ -4138,7 +4138,7 @@
       </c>
       <c r="D162" t="inlineStr"/>
       <c r="E162" t="n">
-        <v>0</v>
+        <v>0.006211376036453782</v>
       </c>
       <c r="F162" t="n">
         <v>-0.07662687086627284</v>
@@ -4165,7 +4165,7 @@
       </c>
       <c r="D163" t="inlineStr"/>
       <c r="E163" t="n">
-        <v>0.0009309131155126528</v>
+        <v>0.005042315513268596</v>
       </c>
       <c r="F163" t="n">
         <v>-0.07927359680981577</v>
@@ -4192,7 +4192,7 @@
       </c>
       <c r="D164" t="inlineStr"/>
       <c r="E164" t="n">
-        <v>0</v>
+        <v>-0.002784459008039621</v>
       </c>
       <c r="F164" t="n">
         <v>0.02678035008665758</v>
@@ -4219,7 +4219,7 @@
       </c>
       <c r="D165" t="inlineStr"/>
       <c r="E165" t="n">
-        <v>0</v>
+        <v>-0.006004577903281553</v>
       </c>
       <c r="F165" t="n">
         <v>0.02366527746145219</v>
@@ -4246,7 +4246,7 @@
       </c>
       <c r="D166" t="inlineStr"/>
       <c r="E166" t="n">
-        <v>-0.002108613610004985</v>
+        <v>-0.008737832289355643</v>
       </c>
       <c r="F166" t="n">
         <v>0.08709702259368868</v>
@@ -4273,7 +4273,7 @@
       </c>
       <c r="D167" t="inlineStr"/>
       <c r="E167" t="n">
-        <v>0.0004767869985814667</v>
+        <v>0.01142333626202555</v>
       </c>
       <c r="F167" t="n">
         <v>-0.07636829095303405</v>
@@ -4300,7 +4300,7 @@
       </c>
       <c r="D168" t="inlineStr"/>
       <c r="E168" t="n">
-        <v>0.004127452090353234</v>
+        <v>0.003365101187823908</v>
       </c>
       <c r="F168" t="n">
         <v>-0.03972424366793509</v>
@@ -4327,7 +4327,7 @@
       </c>
       <c r="D169" t="inlineStr"/>
       <c r="E169" t="n">
-        <v>0.0005635933722142772</v>
+        <v>0.0001318619997788035</v>
       </c>
       <c r="F169" t="n">
         <v>0.01703973350526689</v>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="D170" t="inlineStr"/>
       <c r="E170" t="n">
-        <v>0</v>
+        <v>0.001565041830608065</v>
       </c>
       <c r="F170" t="n">
         <v>-0.02218501325457978</v>
@@ -4381,7 +4381,7 @@
       </c>
       <c r="D171" t="inlineStr"/>
       <c r="E171" t="n">
-        <v>0</v>
+        <v>0.002586205121286455</v>
       </c>
       <c r="F171" t="n">
         <v>-0.01632456510179936</v>
@@ -4408,7 +4408,7 @@
       </c>
       <c r="D172" t="inlineStr"/>
       <c r="E172" t="n">
-        <v>-0.0009861235775864403</v>
+        <v>-0.003858587783503757</v>
       </c>
       <c r="F172" t="n">
         <v>0.02116804159733721</v>
@@ -4435,7 +4435,7 @@
       </c>
       <c r="D173" t="inlineStr"/>
       <c r="E173" t="n">
-        <v>0</v>
+        <v>0.001574021251727816</v>
       </c>
       <c r="F173" t="n">
         <v>-0.004143656724531986</v>
@@ -4462,7 +4462,7 @@
       </c>
       <c r="D174" t="inlineStr"/>
       <c r="E174" t="n">
-        <v>0</v>
+        <v>0.0004209739901591461</v>
       </c>
       <c r="F174" t="n">
         <v>0.0009939303736365979</v>
@@ -4489,7 +4489,7 @@
       </c>
       <c r="D175" t="inlineStr"/>
       <c r="E175" t="n">
-        <v>0.0001586032474507261</v>
+        <v>-0.0007880902917137354</v>
       </c>
       <c r="F175" t="n">
         <v>0.02269488576111367</v>
@@ -4516,7 +4516,7 @@
       </c>
       <c r="D176" t="inlineStr"/>
       <c r="E176" t="n">
-        <v>0</v>
+        <v>0.003670067844600182</v>
       </c>
       <c r="F176" t="n">
         <v>0.05547597056787301</v>
@@ -4543,7 +4543,7 @@
       </c>
       <c r="D177" t="inlineStr"/>
       <c r="E177" t="n">
-        <v>0</v>
+        <v>0.002698395599144366</v>
       </c>
       <c r="F177" t="n">
         <v>-0.0138865133424248</v>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="D178" t="inlineStr"/>
       <c r="E178" t="n">
-        <v>-0.002870916892509833</v>
+        <v>-0.003204404514372242</v>
       </c>
       <c r="F178" t="n">
         <v>-0.004293529713769506</v>
@@ -4597,7 +4597,7 @@
       </c>
       <c r="D179" t="inlineStr"/>
       <c r="E179" t="n">
-        <v>0</v>
+        <v>0.0005114816571303463</v>
       </c>
       <c r="F179" t="n">
         <v>-0.05150016546812169</v>
@@ -4624,7 +4624,7 @@
       </c>
       <c r="D180" t="inlineStr"/>
       <c r="E180" t="n">
-        <v>0</v>
+        <v>-0.003162931091731539</v>
       </c>
       <c r="F180" t="n">
         <v>-0.01916203210456191</v>
@@ -4651,7 +4651,7 @@
       </c>
       <c r="D181" t="inlineStr"/>
       <c r="E181" t="n">
-        <v>-8.802776601805505e-05</v>
+        <v>0.004090349074945928</v>
       </c>
       <c r="F181" t="n">
         <v>-0.009786456235589158</v>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="D182" t="inlineStr"/>
       <c r="E182" t="n">
-        <v>0</v>
+        <v>0.0006092887123389757</v>
       </c>
       <c r="F182" t="n">
         <v>0.02991977929968476</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="D183" t="inlineStr"/>
       <c r="E183" t="n">
-        <v>0</v>
+        <v>-0.001812718485247951</v>
       </c>
       <c r="F183" t="n">
         <v>0.06719883925060965</v>
